--- a/AAII_Financials/Quarterly/NORD_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NORD_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
   <si>
     <t>NORD</t>
   </si>
@@ -656,106 +656,110 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -768,8 +772,8 @@
       <c r="F8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="3">
-        <v>0</v>
+      <c r="G8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H8" s="3">
         <v>0</v>
@@ -777,14 +781,14 @@
       <c r="I8" s="3">
         <v>0</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>4</v>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>4</v>
@@ -792,8 +796,8 @@
       <c r="N8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -819,8 +823,11 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -884,8 +891,11 @@
       <c r="W9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -898,8 +908,8 @@
       <c r="F10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="3">
-        <v>0</v>
+      <c r="G10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
@@ -907,14 +917,14 @@
       <c r="I10" s="3">
         <v>0</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>4</v>
+      <c r="J10" s="3">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>4</v>
@@ -949,8 +959,11 @@
       <c r="W10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,32 +987,33 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3">
         <v>400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,26 +1121,29 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>4</v>
       </c>
@@ -1145,14 +1165,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1166,11 +1186,14 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1234,8 +1257,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,34 +1282,35 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>300</v>
-      </c>
-      <c r="K17" s="3">
-        <v>100</v>
       </c>
       <c r="L17" s="3">
         <v>100</v>
@@ -1295,61 +1322,64 @@
         <v>100</v>
       </c>
       <c r="O17" s="3">
+        <v>100</v>
+      </c>
+      <c r="P17" s="3">
         <v>2500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
       <c r="R17" s="3">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3">
         <v>5000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
       <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
         <v>100</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
       <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-300</v>
       </c>
-      <c r="K18" s="3">
-        <v>-100</v>
-      </c>
       <c r="L18" s="3">
         <v>-100</v>
       </c>
@@ -1360,34 +1390,37 @@
         <v>-100</v>
       </c>
       <c r="O18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P18" s="3">
         <v>-2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-900</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
       <c r="R18" s="3">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3">
         <v>-5000</v>
       </c>
-      <c r="S18" s="3">
-        <v>-100</v>
-      </c>
       <c r="T18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U18" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V18" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W18" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1444,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1422,29 +1456,29 @@
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-100</v>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1476,35 +1510,38 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1200</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-800</v>
       </c>
       <c r="G21" s="3">
         <v>-800</v>
       </c>
       <c r="H21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
-        <v>-100</v>
-      </c>
       <c r="L21" s="3">
         <v>-100</v>
       </c>
@@ -1512,51 +1549,54 @@
         <v>-100</v>
       </c>
       <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P21" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3">
         <v>-900</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
       <c r="R21" s="3">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3">
         <v>-5000</v>
       </c>
-      <c r="S21" s="3">
-        <v>-100</v>
-      </c>
       <c r="T21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U21" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V21" s="3">
-        <v>0</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+        <v>-100</v>
+      </c>
+      <c r="W21" s="3">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
+      <c r="E22" s="3">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -1564,8 +1604,8 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>4</v>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>4</v>
@@ -1579,11 +1619,11 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>4</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>4</v>
@@ -1597,8 +1637,8 @@
       <c r="T22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1606,35 +1646,38 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-300</v>
       </c>
-      <c r="K23" s="3">
-        <v>-100</v>
-      </c>
       <c r="L23" s="3">
         <v>-100</v>
       </c>
@@ -1642,37 +1685,40 @@
         <v>-100</v>
       </c>
       <c r="N23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O23" s="3">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
         <v>-2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-900</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
       <c r="R23" s="3">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3">
         <v>-5000</v>
       </c>
-      <c r="S23" s="3">
-        <v>-100</v>
-      </c>
       <c r="T23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U23" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V23" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W23" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1709,8 +1755,8 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1736,8 +1782,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,35 +1850,38 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="K26" s="3">
-        <v>-100</v>
-      </c>
       <c r="L26" s="3">
         <v>-100</v>
       </c>
@@ -1837,64 +1889,67 @@
         <v>-100</v>
       </c>
       <c r="N26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O26" s="3">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
         <v>-2500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-900</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
       <c r="R26" s="3">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3">
         <v>-5000</v>
       </c>
-      <c r="S26" s="3">
-        <v>-100</v>
-      </c>
       <c r="T26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U26" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V26" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W26" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="K27" s="3">
-        <v>-100</v>
-      </c>
       <c r="L27" s="3">
         <v>-100</v>
       </c>
@@ -1902,37 +1957,40 @@
         <v>-100</v>
       </c>
       <c r="N27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O27" s="3">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3">
         <v>-2500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-900</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
       <c r="R27" s="3">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3">
         <v>-5000</v>
       </c>
-      <c r="S27" s="3">
-        <v>-100</v>
-      </c>
       <c r="T27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U27" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V27" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W27" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2052,17 +2113,20 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>4</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2258,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2202,29 +2272,29 @@
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2256,35 +2326,38 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="K33" s="3">
-        <v>-100</v>
-      </c>
       <c r="L33" s="3">
         <v>-100</v>
       </c>
@@ -2292,37 +2365,40 @@
         <v>-100</v>
       </c>
       <c r="N33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O33" s="3">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3">
         <v>-2500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-900</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
       <c r="R33" s="3">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3">
         <v>-5000</v>
       </c>
-      <c r="S33" s="3">
-        <v>-100</v>
-      </c>
       <c r="T33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U33" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V33" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W33" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,35 +2462,38 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="K35" s="3">
-        <v>-100</v>
-      </c>
       <c r="L35" s="3">
         <v>-100</v>
       </c>
@@ -2422,107 +2501,113 @@
         <v>-100</v>
       </c>
       <c r="N35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O35" s="3">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3">
         <v>-2500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-900</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
       <c r="R35" s="3">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3">
         <v>-5000</v>
       </c>
-      <c r="S35" s="3">
-        <v>-100</v>
-      </c>
       <c r="T35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U35" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V35" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W35" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,19 +2657,20 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E41" s="3">
         <v>200</v>
       </c>
       <c r="F41" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G41" s="3">
         <v>0</v>
@@ -2619,25 +2706,28 @@
         <v>0</v>
       </c>
       <c r="R41" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S41" s="3">
         <v>200</v>
       </c>
       <c r="T41" s="3">
+        <v>200</v>
+      </c>
+      <c r="U41" s="3">
         <v>100</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
       <c r="V41" s="3">
         <v>0</v>
       </c>
       <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,8 +2791,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2739,11 +2832,11 @@
       <c r="N43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>4</v>
+      <c r="O43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>4</v>
@@ -2757,8 +2850,8 @@
       <c r="T43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
@@ -2766,8 +2859,11 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2804,8 +2900,8 @@
       <c r="N44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2831,8 +2927,11 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2869,8 +2968,8 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -2884,8 +2983,8 @@
       <c r="S45" s="3">
         <v>0</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>4</v>
+      <c r="T45" s="3">
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>4</v>
@@ -2893,25 +2992,28 @@
       <c r="V45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>500</v>
+      </c>
+      <c r="E46" s="3">
         <v>600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>200</v>
-      </c>
-      <c r="G46" s="3">
-        <v>100</v>
       </c>
       <c r="H46" s="3">
         <v>100</v>
@@ -2923,7 +3025,7 @@
         <v>100</v>
       </c>
       <c r="K46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L46" s="3">
         <v>0</v>
@@ -2935,51 +3037,54 @@
         <v>0</v>
       </c>
       <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3">
         <v>100</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
       <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3">
         <v>200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>100</v>
       </c>
-      <c r="U46" s="3">
-        <v>0</v>
-      </c>
       <c r="V46" s="3">
         <v>0</v>
       </c>
       <c r="W46" s="3">
+        <v>0</v>
+      </c>
+      <c r="X46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E47" s="3">
         <v>1100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1900</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1800</v>
       </c>
       <c r="I47" s="3">
         <v>1800</v>
@@ -2999,8 +3104,8 @@
       <c r="N47" s="3">
         <v>1800</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
+      <c r="O47" s="3">
+        <v>1800</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>4</v>
@@ -3017,8 +3122,8 @@
       <c r="T47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3026,8 +3131,11 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3037,8 +3145,8 @@
       <c r="E48" s="3">
         <v>0</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>4</v>
+      <c r="F48" s="3">
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>4</v>
@@ -3064,8 +3172,8 @@
       <c r="N48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -3091,35 +3199,38 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>74100</v>
+        <v>72700</v>
       </c>
       <c r="E49" s="3">
         <v>74100</v>
       </c>
       <c r="F49" s="3">
+        <v>74100</v>
+      </c>
+      <c r="G49" s="3">
         <v>74400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>68200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>57800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>18900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18700</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
@@ -3132,8 +3243,8 @@
       <c r="O49" s="3">
         <v>0</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>4</v>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>4</v>
@@ -3147,8 +3258,8 @@
       <c r="T49" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,8 +3403,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3298,23 +3418,23 @@
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
         <v>100</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>300</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
@@ -3324,8 +3444,8 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -3351,8 +3471,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,34 +3539,37 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>75900</v>
+        <v>75500</v>
       </c>
       <c r="E54" s="3">
         <v>75900</v>
       </c>
       <c r="F54" s="3">
+        <v>75900</v>
+      </c>
+      <c r="G54" s="3">
         <v>76100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>70200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>59700</v>
-      </c>
-      <c r="I54" s="3">
-        <v>20800</v>
       </c>
       <c r="J54" s="3">
         <v>20800</v>
       </c>
       <c r="K54" s="3">
-        <v>1800</v>
+        <v>20800</v>
       </c>
       <c r="L54" s="3">
         <v>1800</v>
@@ -3455,34 +3581,37 @@
         <v>1800</v>
       </c>
       <c r="O54" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P54" s="3">
         <v>100</v>
       </c>
-      <c r="P54" s="3">
-        <v>0</v>
-      </c>
       <c r="Q54" s="3">
         <v>0</v>
       </c>
       <c r="R54" s="3">
+        <v>0</v>
+      </c>
+      <c r="S54" s="3">
         <v>200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>100</v>
       </c>
-      <c r="U54" s="3">
-        <v>0</v>
-      </c>
       <c r="V54" s="3">
         <v>0</v>
       </c>
       <c r="W54" s="3">
+        <v>0</v>
+      </c>
+      <c r="X54" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,34 +3661,35 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>600</v>
-      </c>
-      <c r="I57" s="3">
-        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -3585,24 +3716,27 @@
         <v>0</v>
       </c>
       <c r="T57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U57" s="3">
         <v>100</v>
       </c>
       <c r="V57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -3634,14 +3768,14 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>4</v>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>4</v>
@@ -3661,8 +3795,11 @@
       <c r="W58" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3678,20 +3815,20 @@
       <c r="G59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L59" s="3">
+        <v>0</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
@@ -3699,8 +3836,8 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P59" s="3">
         <v>0</v>
@@ -3714,8 +3851,8 @@
       <c r="S59" s="3">
         <v>0</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>4</v>
+      <c r="T59" s="3">
+        <v>0</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>4</v>
@@ -3723,44 +3860,47 @@
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E60" s="3">
         <v>900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>100</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3">
         <v>100</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -3768,16 +3908,16 @@
         <v>0</v>
       </c>
       <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3">
         <v>100</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
       <c r="S60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T60" s="3">
         <v>100</v>
@@ -3786,13 +3926,16 @@
         <v>100</v>
       </c>
       <c r="V60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3856,8 +3999,11 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3894,8 +4040,8 @@
       <c r="N62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -3921,8 +4067,11 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,41 +4271,44 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E66" s="3">
         <v>11100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>100</v>
       </c>
-      <c r="K66" s="3">
-        <v>0</v>
-      </c>
       <c r="L66" s="3">
+        <v>0</v>
+      </c>
+      <c r="M66" s="3">
         <v>100</v>
       </c>
-      <c r="M66" s="3">
-        <v>0</v>
-      </c>
       <c r="N66" s="3">
         <v>0</v>
       </c>
@@ -4158,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="P66" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="3">
         <v>100</v>
       </c>
-      <c r="Q66" s="3">
-        <v>0</v>
-      </c>
       <c r="R66" s="3">
         <v>0</v>
       </c>
       <c r="S66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T66" s="3">
         <v>100</v>
@@ -4176,13 +4334,16 @@
         <v>100</v>
       </c>
       <c r="V66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-50800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-50700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-49500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-48000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-46800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-46200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-44600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-44100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-43900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-42400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-42300</v>
-      </c>
-      <c r="N72" s="3">
-        <v>-42200</v>
       </c>
       <c r="O72" s="3">
         <v>-42200</v>
       </c>
       <c r="P72" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-39700</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>-38800</v>
       </c>
       <c r="R72" s="3">
         <v>-38800</v>
       </c>
       <c r="S72" s="3">
-        <v>-33700</v>
+        <v>-38800</v>
       </c>
       <c r="T72" s="3">
         <v>-33700</v>
       </c>
       <c r="U72" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="V72" s="3">
         <v>-33600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-33500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-33400</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,47 +4909,50 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>64300</v>
+      </c>
+      <c r="E76" s="3">
         <v>64800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>64700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>64300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>59900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>58800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1800</v>
-      </c>
-      <c r="L76" s="3">
-        <v>1700</v>
       </c>
       <c r="M76" s="3">
         <v>1700</v>
       </c>
       <c r="N76" s="3">
+        <v>1700</v>
+      </c>
+      <c r="O76" s="3">
         <v>1800</v>
       </c>
-      <c r="O76" s="3">
-        <v>0</v>
-      </c>
       <c r="P76" s="3">
         <v>0</v>
       </c>
@@ -4774,25 +4960,28 @@
         <v>0</v>
       </c>
       <c r="R76" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="S76" s="3">
         <v>200</v>
       </c>
       <c r="T76" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="U76" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W76" s="3">
+        <v>0</v>
+      </c>
+      <c r="X76" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,105 +5045,111 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="K81" s="3">
-        <v>-100</v>
-      </c>
       <c r="L81" s="3">
         <v>-100</v>
       </c>
@@ -4962,37 +5157,40 @@
         <v>-100</v>
       </c>
       <c r="N81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O81" s="3">
+        <v>0</v>
+      </c>
+      <c r="P81" s="3">
         <v>-2500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-900</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
       <c r="R81" s="3">
+        <v>0</v>
+      </c>
+      <c r="S81" s="3">
         <v>-5000</v>
       </c>
-      <c r="S81" s="3">
-        <v>-100</v>
-      </c>
       <c r="T81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U81" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="V81" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W81" s="3">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,8 +5214,9 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5060,8 +5259,8 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -5081,8 +5280,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,35 +5620,38 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1800</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-400</v>
       </c>
       <c r="G89" s="3">
         <v>-400</v>
       </c>
       <c r="H89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="K89" s="3">
-        <v>-100</v>
-      </c>
       <c r="L89" s="3">
         <v>-100</v>
       </c>
@@ -5442,19 +5659,19 @@
         <v>-100</v>
       </c>
       <c r="N89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-200</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
       <c r="Q89" s="3">
         <v>0</v>
       </c>
       <c r="R89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="S89" s="3">
         <v>-100</v>
@@ -5463,16 +5680,19 @@
         <v>-100</v>
       </c>
       <c r="U89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W89" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,8 +5716,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5507,8 +5728,8 @@
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
+      <c r="F91" s="3">
+        <v>0</v>
       </c>
       <c r="G91" s="3" t="s">
         <v>4</v>
@@ -5534,8 +5755,8 @@
       <c r="N91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -5561,8 +5782,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,8 +5918,11 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5702,11 +5932,11 @@
       <c r="E94" s="3">
         <v>0</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -5715,11 +5945,11 @@
         <v>0</v>
       </c>
       <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>100</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
@@ -5735,8 +5965,8 @@
       <c r="P94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -5756,8 +5986,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5807,20 +6041,20 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
+      <c r="M96" s="3">
+        <v>0</v>
       </c>
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,31 +6284,34 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>500</v>
+      </c>
+      <c r="E100" s="3">
         <v>1400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>400</v>
-      </c>
-      <c r="G100" s="3">
-        <v>300</v>
       </c>
       <c r="H100" s="3">
         <v>300</v>
       </c>
       <c r="I100" s="3">
+        <v>300</v>
+      </c>
+      <c r="J100" s="3">
         <v>400</v>
-      </c>
-      <c r="J100" s="3">
-        <v>100</v>
       </c>
       <c r="K100" s="3">
         <v>100</v>
@@ -6077,28 +6323,28 @@
         <v>100</v>
       </c>
       <c r="N100" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>4</v>
+      <c r="Q100" s="3">
+        <v>0</v>
       </c>
       <c r="R100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S100" s="3">
-        <v>200</v>
+      <c r="S100" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T100" s="3">
         <v>200</v>
       </c>
       <c r="U100" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="V100" s="3">
         <v>0</v>
@@ -6106,16 +6352,19 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -6135,8 +6384,8 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>4</v>
@@ -6162,8 +6411,8 @@
       <c r="T101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -6171,20 +6420,23 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
         <v>0</v>
       </c>
@@ -6216,24 +6468,27 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
-        <v>-100</v>
-      </c>
       <c r="S102" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="T102" s="3">
         <v>100</v>
       </c>
       <c r="U102" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
     </row>
